--- a/backend/assessment_bank_exports/问卷_第2份.xlsx
+++ b/backend/assessment_bank_exports/问卷_第2份.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CoWorkProjects\IntelligentMoralEducationWhole-processSystem1.0\backend\assessment_bank_exports\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luoxu\.codex\worktrees\2c1f\IntelligentMoralEducationWhole-processSystem1.0\backend\assessment_bank_exports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76FE81CC-4C3B-4E8F-A353-1B68C6B5E629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{007B5E78-AA1D-4B44-9AED-8935666FC7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="6090" yWindow="2490" windowWidth="28800" windowHeight="15420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4368,7 +4368,7 @@
         <v>46</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>247</v>
